--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle_Mestre" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,21 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,100 +413,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Codigo_ECO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Titulo_Alteracao</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Area_Solicitante</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Nome_Engenheiro_Responsavel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Email_Solicitante</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Data_Recebimento</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Nivel_Prioridade</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Status_Atual</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justificativa_Tecnica</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Codigo_Item_Afetado</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Categoria_Mudanca</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Impacto_Custos</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Estimativa_Orcamento</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Unidade_Fabril</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Data_Implementacao_Alvo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Status_Automacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
         </is>
       </c>
     </row>

--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,22 +707,250 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Manaus</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>

--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,8 +707,10 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -721,236 +723,6 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
-        <is>
-          <t>REGISTRADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ECO-00126</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Alteração dimensional do suporte</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Carlos Lima</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>carlos.lima@matriz.example</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SUP-778</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Componente</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Manaus</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>PENDENTE_VALIDACAO_HUMANA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ECO-00127</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Atualização urgente de firmware</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Engenharia de Software</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Bruno Costa</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>bruno.costa@matriz.example</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Correção emergencial de firmware.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>FW-900</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>-500</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Manaus</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>BLOQUEADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ECO-00125</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Atualização do layout do módulo de refrigeração</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ana Souza</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ana.souza@matriz.example</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ITEM-REF-220</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Layout</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Manaus</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>

--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,22 +707,478 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ERRO_SISTEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ERRO_SISTEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Manaus</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>

--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,22 +1163,478 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Manaus</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>

--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,22 +1619,2074 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Manaus</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>

--- a/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
+++ b/02_AUTOMACAO_ECOS/data/controle_mestre_ecos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3671,22 +3671,478 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>REGISTRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ECO-00126</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alteração dimensional do suporte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Carlos Lima</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>carlos.lima@matriz.example</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SUP-778</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>3500</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PENDENTE_VALIDACAO_HUMANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ECO-00127</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Atualização urgente de firmware</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>bruno.costa@matriz.example</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Correção emergencial de firmware.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>FW-900</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-500</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>BLOQUEADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ECO-00125</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Atualização do layout do módulo de refrigeração</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Engenharia</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ana Souza</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ana.souza@matriz.example</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Recebido</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Adequação do posicionamento do componente para melhoria de montagem.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ITEM-REF-220</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Layout</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Manaus</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Manaus</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>REGISTRADO</t>
         </is>
